--- a/src/test/resources/testData/testdata.xlsx
+++ b/src/test/resources/testData/testdata.xlsx
@@ -5,15 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2497768\IdeaProjects\Hackathon-Project\src\test\resources\testData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2497810\eclipse-workspace\Hackathon-Project\src\test\resources\testData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B5FB2C2-B198-420E-A805-6F748AAF9F42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30950EE5-971A-467D-BDA7-BFB2E10978C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PractoData" sheetId="1" r:id="rId1"/>
+    <sheet name="HospitalTestData" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="32">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -94,13 +95,40 @@
   </si>
   <si>
     <t>TC_002</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>RequiredMatchCount</t>
+  </si>
+  <si>
+    <t>MinimumRating</t>
+  </si>
+  <si>
+    <t>TC11</t>
+  </si>
+  <si>
+    <t>TC12</t>
+  </si>
+  <si>
+    <t>TC13</t>
+  </si>
+  <si>
+    <t>TC14</t>
+  </si>
+  <si>
+    <t>TC15</t>
+  </si>
+  <si>
+    <t>hospital 24/7</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -138,8 +166,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -152,8 +193,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F5F5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -161,17 +208,38 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFE6E6E6"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFE6E6E6"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFE6E6E6"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFE6E6E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -576,4 +644,106 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09CAE19C-3C30-4587-96DE-D311C191F8C9}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="23.6328125" customWidth="1"/>
+    <col min="3" max="3" width="20.08984375" customWidth="1"/>
+    <col min="4" max="4" width="27.26953125" customWidth="1"/>
+    <col min="5" max="5" width="39.26953125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+    </row>
+    <row r="3" spans="1:5" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="6">
+        <v>10</v>
+      </c>
+      <c r="E3" s="6">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+    </row>
+    <row r="5" spans="1:5" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+    </row>
+    <row r="6" spans="1:5" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/test/resources/testData/testdata.xlsx
+++ b/src/test/resources/testData/testdata.xlsx
@@ -5,16 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2497810\eclipse-workspace\Hackathon-Project\src\test\resources\testData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2497808\IdeaProjects\Hackathon-Project\src\test\resources\testData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30950EE5-971A-467D-BDA7-BFB2E10978C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EC2338D-9BD6-49B0-BE85-BA6902E1A6D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4020" yWindow="3110" windowWidth="14400" windowHeight="8170" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PractoData" sheetId="1" r:id="rId1"/>
     <sheet name="HospitalTestData" sheetId="2" r:id="rId2"/>
+    <sheet name="MedicineData" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="35">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -122,6 +123,15 @@
   </si>
   <si>
     <t>hospital 24/7</t>
+  </si>
+  <si>
+    <t>skin ointment</t>
+  </si>
+  <si>
+    <t>TC_017</t>
+  </si>
+  <si>
+    <t>SearchMedicine</t>
   </si>
 </sst>
 </file>
@@ -200,7 +210,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -223,12 +233,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFE6E6E6"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFE6E6E6"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -238,6 +259,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -648,16 +675,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09CAE19C-3C30-4587-96DE-D311C191F8C9}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="23.6328125" customWidth="1"/>
     <col min="3" max="3" width="20.08984375" customWidth="1"/>
     <col min="4" max="4" width="27.26953125" customWidth="1"/>
     <col min="5" max="5" width="39.26953125" customWidth="1"/>
+    <col min="6" max="6" width="24" customWidth="1"/>
+    <col min="7" max="7" width="21.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -673,8 +702,9 @@
       <c r="E1" s="5" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="F1" s="7"/>
+    </row>
+    <row r="2" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="6" t="s">
         <v>26</v>
       </c>
@@ -686,8 +716,9 @@
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
-    </row>
-    <row r="3" spans="1:5" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="F2" s="8"/>
+    </row>
+    <row r="3" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="6" t="s">
         <v>27</v>
       </c>
@@ -704,7 +735,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:6" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="6" t="s">
         <v>28</v>
       </c>
@@ -717,7 +748,7 @@
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
     </row>
-    <row r="5" spans="1:5" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:6" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="6" t="s">
         <v>29</v>
       </c>
@@ -730,7 +761,7 @@
       <c r="D5" s="6"/>
       <c r="E5" s="6"/>
     </row>
-    <row r="6" spans="1:5" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:6" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="6" t="s">
         <v>30</v>
       </c>
@@ -742,6 +773,36 @@
       </c>
       <c r="D6" s="6"/>
       <c r="E6" s="6"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE4B8614-B6CB-4959-8F28-25784C056AAF}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="23.6328125" customWidth="1"/>
+    <col min="2" max="2" width="23" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" t="s">
+        <v>32</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/test/resources/testData/testdata.xlsx
+++ b/src/test/resources/testData/testdata.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2497808\IdeaProjects\Hackathon-Project\src\test\resources\testData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2497768\IdeaProjects\Hackathon-Project\src\test\resources\testData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EC2338D-9BD6-49B0-BE85-BA6902E1A6D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27FF9F97-B3A6-4369-9F43-238AD2BF66D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4020" yWindow="3110" windowWidth="14400" windowHeight="8170" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PractoData" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="36">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -132,6 +132,9 @@
   </si>
   <si>
     <t>SearchMedicine</t>
+  </si>
+  <si>
+    <t>TC_018</t>
   </si>
 </sst>
 </file>
@@ -658,6 +661,17 @@
         <v>14</v>
       </c>
     </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>35</v>
+      </c>
+      <c r="I4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4">
+        <v>3728499</v>
+      </c>
+    </row>
     <row r="7" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="C7" s="1"/>
     </row>

--- a/src/test/resources/testData/testdata.xlsx
+++ b/src/test/resources/testData/testdata.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2497808\IdeaProjects\Hackathon-Project\src\test\resources\testData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2497810\eclipse-workspace\Hackathon-Project\src\test\resources\testData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EC2338D-9BD6-49B0-BE85-BA6902E1A6D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A6DB6E6-7328-431F-83D6-3BBCC92CDAB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4020" yWindow="3110" windowWidth="14400" windowHeight="8170" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PractoData" sheetId="1" r:id="rId1"/>
@@ -735,7 +735,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="6" t="s">
         <v>28</v>
       </c>

--- a/src/test/resources/testData/testdata.xlsx
+++ b/src/test/resources/testData/testdata.xlsx
@@ -8,14 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2497808\IdeaProjects\Hackathon-Project\src\test\resources\testData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EC2338D-9BD6-49B0-BE85-BA6902E1A6D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F4F7FAA-A283-4A03-88C2-88970B8D8BA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4020" yWindow="3110" windowWidth="14400" windowHeight="8170" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PractoData" sheetId="1" r:id="rId1"/>
     <sheet name="HospitalTestData" sheetId="2" r:id="rId2"/>
     <sheet name="MedicineData" sheetId="3" r:id="rId3"/>
+    <sheet name="CorporateData" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet2" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="49">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -132,6 +134,48 @@
   </si>
   <si>
     <t>SearchMedicine</t>
+  </si>
+  <si>
+    <t>TC_018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_019 </t>
+  </si>
+  <si>
+    <t>invalidmedicine123</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Organization</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OrganizationSize </t>
+  </si>
+  <si>
+    <t>InterestedIn</t>
+  </si>
+  <si>
+    <t>TC_020</t>
+  </si>
+  <si>
+    <t>Test User</t>
+  </si>
+  <si>
+    <t>Cognizant</t>
+  </si>
+  <si>
+    <t>cognizant.com</t>
+  </si>
+  <si>
+    <t>&lt;500</t>
+  </si>
+  <si>
+    <t>Taking a demo</t>
   </si>
 </sst>
 </file>
@@ -781,7 +825,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE4B8614-B6CB-4959-8F28-25784C056AAF}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="23.6328125" customWidth="1"/>
@@ -804,7 +848,97 @@
         <v>32</v>
       </c>
     </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" t="s">
+        <v>37</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE5D347C-216E-4A10-8971-EEED39DA2512}">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="16.1796875" customWidth="1"/>
+    <col min="2" max="2" width="17.7265625" customWidth="1"/>
+    <col min="3" max="3" width="19.36328125" customWidth="1"/>
+    <col min="4" max="4" width="18.1796875" customWidth="1"/>
+    <col min="5" max="5" width="17" customWidth="1"/>
+    <col min="6" max="6" width="23.54296875" customWidth="1"/>
+    <col min="7" max="7" width="23.26953125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E2">
+        <v>878267565</v>
+      </c>
+      <c r="F2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D44184D5-17C1-412E-B340-0B50DE6DA8E5}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/test/resources/testData/testdata.xlsx
+++ b/src/test/resources/testData/testdata.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2497768\IdeaProjects\Hackathon-Project\src\test\resources\testData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27FF9F97-B3A6-4369-9F43-238AD2BF66D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A49CF92-128B-4DAD-8A8B-0D29610B2032}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PractoData" sheetId="1" r:id="rId1"/>
-    <sheet name="HospitalTestData" sheetId="2" r:id="rId2"/>
-    <sheet name="MedicineData" sheetId="3" r:id="rId3"/>
+    <sheet name="CitySearch" sheetId="4" r:id="rId2"/>
+    <sheet name="HospitalTestData" sheetId="2" r:id="rId3"/>
+    <sheet name="MedicineData" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="38">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -135,6 +136,12 @@
   </si>
   <si>
     <t>TC_018</t>
+  </si>
+  <si>
+    <t>TC_008</t>
+  </si>
+  <si>
+    <t>CityName</t>
   </si>
 </sst>
 </file>
@@ -688,6 +695,35 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1463F736-355C-4F92-93B0-AF89C4FB4BBE}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="13.26953125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09CAE19C-3C30-4587-96DE-D311C191F8C9}">
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -793,7 +829,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE4B8614-B6CB-4959-8F28-25784C056AAF}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>

--- a/src/test/resources/testData/testdata.xlsx
+++ b/src/test/resources/testData/testdata.xlsx
@@ -8,14 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2497768\IdeaProjects\Hackathon-Project\src\test\resources\testData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27FF9F97-B3A6-4369-9F43-238AD2BF66D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3DCD46E-1C22-4431-AEFB-2CBA6D02E69E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PractoData" sheetId="1" r:id="rId1"/>
-    <sheet name="HospitalTestData" sheetId="2" r:id="rId2"/>
-    <sheet name="MedicineData" sheetId="3" r:id="rId3"/>
+    <sheet name="CitySearch" sheetId="4" r:id="rId2"/>
+    <sheet name="HospitalTestData" sheetId="2" r:id="rId3"/>
+    <sheet name="MedicineData" sheetId="3" r:id="rId4"/>
+    <sheet name="CorporateData" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,14 +29,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="45">
   <si>
     <t>TestCaseID</t>
   </si>
   <si>
-    <t>City</t>
-  </si>
-  <si>
     <t>SearchKeyword</t>
   </si>
   <si>
@@ -47,94 +46,124 @@
     <t>InvalidPassword</t>
   </si>
   <si>
-    <t>LabCity</t>
-  </si>
-  <si>
-    <t>LabSearch</t>
+    <t>InvalidMobile</t>
+  </si>
+  <si>
+    <t>TC_001</t>
+  </si>
+  <si>
+    <t>Bangalore</t>
+  </si>
+  <si>
+    <t>Hospital</t>
+  </si>
+  <si>
+    <t>WrongPassword123</t>
+  </si>
+  <si>
+    <t>Amruthayadav@30</t>
+  </si>
+  <si>
+    <t>ExpectedProfileName</t>
+  </si>
+  <si>
+    <t>Amrutha</t>
+  </si>
+  <si>
+    <t>TC_002</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>RequiredMatchCount</t>
+  </si>
+  <si>
+    <t>MinimumRating</t>
+  </si>
+  <si>
+    <t>hospital 24/7</t>
+  </si>
+  <si>
+    <t>skin ointment</t>
+  </si>
+  <si>
+    <t>TC_017</t>
+  </si>
+  <si>
+    <t>SearchMedicine</t>
+  </si>
+  <si>
+    <t>TC_018</t>
+  </si>
+  <si>
+    <t>CityName</t>
+  </si>
+  <si>
+    <t>TC_008</t>
+  </si>
+  <si>
+    <t>xyzinvalidmedicine123</t>
+  </si>
+  <si>
+    <t>TC_019</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Organization</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>OrganizationSize</t>
+  </si>
+  <si>
+    <t>InterestedIn</t>
+  </si>
+  <si>
+    <t>Test User</t>
+  </si>
+  <si>
+    <t>Cognizant</t>
+  </si>
+  <si>
+    <t>Cognizant.com</t>
+  </si>
+  <si>
+    <t>&lt;500</t>
+  </si>
+  <si>
+    <t>Taking a demo</t>
+  </si>
+  <si>
+    <t>TC_014</t>
+  </si>
+  <si>
+    <t>TC_005</t>
+  </si>
+  <si>
+    <t>TC_009</t>
+  </si>
+  <si>
+    <t>TC_010</t>
+  </si>
+  <si>
+    <t>TC_011</t>
+  </si>
+  <si>
+    <t>TC_012</t>
+  </si>
+  <si>
+    <t>TC_016</t>
   </si>
   <si>
     <t>Symptom</t>
   </si>
   <si>
-    <t>InvalidMobile</t>
-  </si>
-  <si>
-    <t>MedicineName</t>
-  </si>
-  <si>
-    <t>TC_001</t>
-  </si>
-  <si>
-    <t>Bangalore</t>
-  </si>
-  <si>
-    <t>Hospital</t>
-  </si>
-  <si>
-    <t>WrongPassword123</t>
-  </si>
-  <si>
-    <t>Pune</t>
-  </si>
-  <si>
-    <t>Thyroid</t>
-  </si>
-  <si>
     <t>Fever</t>
-  </si>
-  <si>
-    <t>Paracetamol</t>
-  </si>
-  <si>
-    <t>Amruthayadav@30</t>
-  </si>
-  <si>
-    <t>ExpectedProfileName</t>
-  </si>
-  <si>
-    <t>Amrutha</t>
-  </si>
-  <si>
-    <t>TC_002</t>
-  </si>
-  <si>
-    <t>Location</t>
-  </si>
-  <si>
-    <t>RequiredMatchCount</t>
-  </si>
-  <si>
-    <t>MinimumRating</t>
-  </si>
-  <si>
-    <t>TC11</t>
-  </si>
-  <si>
-    <t>TC12</t>
-  </si>
-  <si>
-    <t>TC13</t>
-  </si>
-  <si>
-    <t>TC14</t>
-  </si>
-  <si>
-    <t>TC15</t>
-  </si>
-  <si>
-    <t>hospital 24/7</t>
-  </si>
-  <si>
-    <t>skin ointment</t>
-  </si>
-  <si>
-    <t>TC_017</t>
-  </si>
-  <si>
-    <t>SearchMedicine</t>
-  </si>
-  <si>
-    <t>TC_018</t>
   </si>
 </sst>
 </file>
@@ -150,22 +179,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -191,6 +206,19 @@
       <color theme="1"/>
       <name val="Segoe UI"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Segoe UI"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -250,26 +278,26 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -551,143 +579,112 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.453125" customWidth="1"/>
-    <col min="2" max="2" width="14.1796875" customWidth="1"/>
-    <col min="3" max="3" width="18.36328125" customWidth="1"/>
-    <col min="4" max="4" width="12.36328125" customWidth="1"/>
-    <col min="5" max="5" width="15.36328125" customWidth="1"/>
-    <col min="6" max="6" width="21.26953125" customWidth="1"/>
-    <col min="7" max="7" width="17.08984375" customWidth="1"/>
-    <col min="8" max="8" width="19" customWidth="1"/>
-    <col min="9" max="9" width="15.26953125" customWidth="1"/>
-    <col min="10" max="10" width="15.6328125" customWidth="1"/>
-    <col min="11" max="11" width="16.7265625" customWidth="1"/>
-    <col min="12" max="12" width="24.36328125" customWidth="1"/>
+    <col min="2" max="2" width="12.36328125" customWidth="1"/>
+    <col min="3" max="3" width="15.36328125" customWidth="1"/>
+    <col min="4" max="4" width="21.26953125" customWidth="1"/>
+    <col min="5" max="5" width="15.26953125" customWidth="1"/>
+    <col min="6" max="6" width="24.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:7" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="F1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="2" t="s">
+      <c r="B2">
+        <v>9346740043</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3">
+        <v>9346740043</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2">
-        <v>9346740043</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2">
-        <v>12345</v>
-      </c>
-      <c r="K2" t="s">
-        <v>18</v>
-      </c>
-      <c r="L2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3">
-        <v>9346740043</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>35</v>
-      </c>
-      <c r="I4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J4">
-        <v>3728499</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="C7" s="1"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="C8" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="E4">
+        <v>24355434</v>
+      </c>
+      <c r="G4" t="s">
+        <v>44</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1" xr:uid="{FFC2F267-70F2-43E4-936E-67873324DA77}"/>
-    <hyperlink ref="E3" r:id="rId2" xr:uid="{3C069D1D-0359-42FF-B429-AB0A744BFCD7}"/>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{FFC2F267-70F2-43E4-936E-67873324DA77}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9291876-DAC6-438D-AF09-0F933D59496B}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultColWidth="20" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09CAE19C-3C30-4587-96DE-D311C191F8C9}">
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -701,101 +698,101 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="5"/>
+    </row>
+    <row r="2" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F1" s="7"/>
-    </row>
-    <row r="2" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="8"/>
+      <c r="B2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="6"/>
     </row>
     <row r="3" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="6">
+      <c r="A3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+    </row>
+    <row r="4" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="4">
         <v>10</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E4" s="4">
         <v>3.5</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-    </row>
-    <row r="5" spans="1:6" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-    </row>
-    <row r="6" spans="1:6" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
+    <row r="5" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+    </row>
+    <row r="6" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE4B8614-B6CB-4959-8F28-25784C056AAF}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="23.6328125" customWidth="1"/>
@@ -807,15 +804,96 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57E3F3F1-ADDA-48B5-AFE9-387D00BC1846}">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.7265625" customWidth="1"/>
+    <col min="2" max="2" width="16.6328125" customWidth="1"/>
+    <col min="3" max="3" width="17.90625" customWidth="1"/>
+    <col min="4" max="4" width="23.453125" customWidth="1"/>
+    <col min="5" max="5" width="21.26953125" customWidth="1"/>
+    <col min="6" max="6" width="29.6328125" customWidth="1"/>
+    <col min="7" max="7" width="23" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="B2" t="s">
-        <v>32</v>
+      <c r="E2" s="8">
+        <v>987654323</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/testData/testdata.xlsx
+++ b/src/test/resources/testData/testdata.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2497768\IdeaProjects\Hackathon-Project\src\test\resources\testData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A49CF92-128B-4DAD-8A8B-0D29610B2032}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3DCD46E-1C22-4431-AEFB-2CBA6D02E69E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PractoData" sheetId="1" r:id="rId1"/>
     <sheet name="CitySearch" sheetId="4" r:id="rId2"/>
     <sheet name="HospitalTestData" sheetId="2" r:id="rId3"/>
     <sheet name="MedicineData" sheetId="3" r:id="rId4"/>
+    <sheet name="CorporateData" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,14 +29,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="45">
   <si>
     <t>TestCaseID</t>
   </si>
   <si>
-    <t>City</t>
-  </si>
-  <si>
     <t>SearchKeyword</t>
   </si>
   <si>
@@ -48,100 +46,124 @@
     <t>InvalidPassword</t>
   </si>
   <si>
-    <t>LabCity</t>
-  </si>
-  <si>
-    <t>LabSearch</t>
+    <t>InvalidMobile</t>
+  </si>
+  <si>
+    <t>TC_001</t>
+  </si>
+  <si>
+    <t>Bangalore</t>
+  </si>
+  <si>
+    <t>Hospital</t>
+  </si>
+  <si>
+    <t>WrongPassword123</t>
+  </si>
+  <si>
+    <t>Amruthayadav@30</t>
+  </si>
+  <si>
+    <t>ExpectedProfileName</t>
+  </si>
+  <si>
+    <t>Amrutha</t>
+  </si>
+  <si>
+    <t>TC_002</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>RequiredMatchCount</t>
+  </si>
+  <si>
+    <t>MinimumRating</t>
+  </si>
+  <si>
+    <t>hospital 24/7</t>
+  </si>
+  <si>
+    <t>skin ointment</t>
+  </si>
+  <si>
+    <t>TC_017</t>
+  </si>
+  <si>
+    <t>SearchMedicine</t>
+  </si>
+  <si>
+    <t>TC_018</t>
+  </si>
+  <si>
+    <t>CityName</t>
+  </si>
+  <si>
+    <t>TC_008</t>
+  </si>
+  <si>
+    <t>xyzinvalidmedicine123</t>
+  </si>
+  <si>
+    <t>TC_019</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Organization</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>OrganizationSize</t>
+  </si>
+  <si>
+    <t>InterestedIn</t>
+  </si>
+  <si>
+    <t>Test User</t>
+  </si>
+  <si>
+    <t>Cognizant</t>
+  </si>
+  <si>
+    <t>Cognizant.com</t>
+  </si>
+  <si>
+    <t>&lt;500</t>
+  </si>
+  <si>
+    <t>Taking a demo</t>
+  </si>
+  <si>
+    <t>TC_014</t>
+  </si>
+  <si>
+    <t>TC_005</t>
+  </si>
+  <si>
+    <t>TC_009</t>
+  </si>
+  <si>
+    <t>TC_010</t>
+  </si>
+  <si>
+    <t>TC_011</t>
+  </si>
+  <si>
+    <t>TC_012</t>
+  </si>
+  <si>
+    <t>TC_016</t>
   </si>
   <si>
     <t>Symptom</t>
   </si>
   <si>
-    <t>InvalidMobile</t>
-  </si>
-  <si>
-    <t>MedicineName</t>
-  </si>
-  <si>
-    <t>TC_001</t>
-  </si>
-  <si>
-    <t>Bangalore</t>
-  </si>
-  <si>
-    <t>Hospital</t>
-  </si>
-  <si>
-    <t>WrongPassword123</t>
-  </si>
-  <si>
-    <t>Pune</t>
-  </si>
-  <si>
-    <t>Thyroid</t>
-  </si>
-  <si>
     <t>Fever</t>
-  </si>
-  <si>
-    <t>Paracetamol</t>
-  </si>
-  <si>
-    <t>Amruthayadav@30</t>
-  </si>
-  <si>
-    <t>ExpectedProfileName</t>
-  </si>
-  <si>
-    <t>Amrutha</t>
-  </si>
-  <si>
-    <t>TC_002</t>
-  </si>
-  <si>
-    <t>Location</t>
-  </si>
-  <si>
-    <t>RequiredMatchCount</t>
-  </si>
-  <si>
-    <t>MinimumRating</t>
-  </si>
-  <si>
-    <t>TC11</t>
-  </si>
-  <si>
-    <t>TC12</t>
-  </si>
-  <si>
-    <t>TC13</t>
-  </si>
-  <si>
-    <t>TC14</t>
-  </si>
-  <si>
-    <t>TC15</t>
-  </si>
-  <si>
-    <t>hospital 24/7</t>
-  </si>
-  <si>
-    <t>skin ointment</t>
-  </si>
-  <si>
-    <t>TC_017</t>
-  </si>
-  <si>
-    <t>SearchMedicine</t>
-  </si>
-  <si>
-    <t>TC_018</t>
-  </si>
-  <si>
-    <t>TC_008</t>
-  </si>
-  <si>
-    <t>CityName</t>
   </si>
 </sst>
 </file>
@@ -157,22 +179,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -198,6 +206,19 @@
       <color theme="1"/>
       <name val="Segoe UI"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Segoe UI"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -257,26 +278,26 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -558,164 +579,104 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.453125" customWidth="1"/>
-    <col min="2" max="2" width="14.1796875" customWidth="1"/>
-    <col min="3" max="3" width="18.36328125" customWidth="1"/>
-    <col min="4" max="4" width="12.36328125" customWidth="1"/>
-    <col min="5" max="5" width="15.36328125" customWidth="1"/>
-    <col min="6" max="6" width="21.26953125" customWidth="1"/>
-    <col min="7" max="7" width="17.08984375" customWidth="1"/>
-    <col min="8" max="8" width="19" customWidth="1"/>
-    <col min="9" max="9" width="15.26953125" customWidth="1"/>
-    <col min="10" max="10" width="15.6328125" customWidth="1"/>
-    <col min="11" max="11" width="16.7265625" customWidth="1"/>
-    <col min="12" max="12" width="24.36328125" customWidth="1"/>
+    <col min="2" max="2" width="12.36328125" customWidth="1"/>
+    <col min="3" max="3" width="15.36328125" customWidth="1"/>
+    <col min="4" max="4" width="21.26953125" customWidth="1"/>
+    <col min="5" max="5" width="15.26953125" customWidth="1"/>
+    <col min="6" max="6" width="24.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:7" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="F1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="2" t="s">
+      <c r="B2">
+        <v>9346740043</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3">
+        <v>9346740043</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2">
-        <v>9346740043</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2">
-        <v>12345</v>
-      </c>
-      <c r="K2" t="s">
-        <v>18</v>
-      </c>
-      <c r="L2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3">
-        <v>9346740043</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>35</v>
-      </c>
-      <c r="I4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J4">
-        <v>3728499</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="C7" s="1"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="C8" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="E4">
+        <v>24355434</v>
+      </c>
+      <c r="G4" t="s">
+        <v>44</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1" xr:uid="{FFC2F267-70F2-43E4-936E-67873324DA77}"/>
-    <hyperlink ref="E3" r:id="rId2" xr:uid="{3C069D1D-0359-42FF-B429-AB0A744BFCD7}"/>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{FFC2F267-70F2-43E4-936E-67873324DA77}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1463F736-355C-4F92-93B0-AF89C4FB4BBE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9291876-DAC6-438D-AF09-0F933D59496B}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="13.26953125" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultColWidth="20" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -737,92 +698,92 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="5"/>
+    </row>
+    <row r="2" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F1" s="7"/>
-    </row>
-    <row r="2" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="8"/>
+      <c r="B2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="6"/>
     </row>
     <row r="3" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="6">
+      <c r="A3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+    </row>
+    <row r="4" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="4">
         <v>10</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E4" s="4">
         <v>3.5</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-    </row>
-    <row r="5" spans="1:6" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-    </row>
-    <row r="6" spans="1:6" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
+    <row r="5" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+    </row>
+    <row r="6" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -831,7 +792,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE4B8614-B6CB-4959-8F28-25784C056AAF}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="23.6328125" customWidth="1"/>
@@ -843,15 +804,96 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57E3F3F1-ADDA-48B5-AFE9-387D00BC1846}">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.7265625" customWidth="1"/>
+    <col min="2" max="2" width="16.6328125" customWidth="1"/>
+    <col min="3" max="3" width="17.90625" customWidth="1"/>
+    <col min="4" max="4" width="23.453125" customWidth="1"/>
+    <col min="5" max="5" width="21.26953125" customWidth="1"/>
+    <col min="6" max="6" width="29.6328125" customWidth="1"/>
+    <col min="7" max="7" width="23" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="B2" t="s">
-        <v>32</v>
+      <c r="E2" s="8">
+        <v>987654323</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
